--- a/files_tests/FORMATO DE CARGA - ING. CIVIL .xlsx
+++ b/files_tests/FORMATO DE CARGA - ING. CIVIL .xlsx
@@ -6,7 +6,7 @@
     <sheet state="visible" name="MALLA Ing. Civil" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'MALLA Ing. Civil'!$A$1:$H$76</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'MALLA Ing. Civil'!$A$1:$H$80</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="31">
   <si>
     <t>Normativa</t>
   </si>
@@ -53,20 +53,20 @@
     <t>Correquisito</t>
   </si>
   <si>
-    <t>OPTATIVA 1</t>
+    <t>OPTATIVA1</t>
   </si>
   <si>
     <t>NO</t>
   </si>
   <si>
-    <t>OPTATIVA 2</t>
+    <t>OPTATIVA2</t>
   </si>
   <si>
     <t xml:space="preserve">4201074
 </t>
   </si>
   <si>
-    <t>OPTATIVA 3</t>
+    <t>OPTATIVA3</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -110,10 +110,10 @@
     <t>LIBRE11</t>
   </si>
   <si>
-    <t>NIVELATORIO 1</t>
+    <t>NIVELATORIO1</t>
   </si>
   <si>
-    <t>NIVELATORIO 2</t>
+    <t>NIVELATORIO2</t>
   </si>
 </sst>
 </file>
@@ -2350,7 +2350,7 @@
       <c r="C75" s="7">
         <v>32.0</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D75" s="6" t="s">
         <v>29</v>
       </c>
       <c r="E75" s="11" t="s">
@@ -2372,7 +2372,7 @@
       <c r="C76" s="7">
         <v>32.0</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D76" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E76" s="11" t="s">
@@ -2385,44 +2385,98 @@
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="16"/>
-      <c r="B77" s="16"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-      <c r="H77" s="18"/>
+      <c r="A77" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B77" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="C77" s="7">
+        <v>30.0</v>
+      </c>
+      <c r="D77" s="7">
+        <v>1000044.0</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" s="15"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="6">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="16"/>
-      <c r="B78" s="16"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16"/>
-      <c r="H78" s="18"/>
+      <c r="A78" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B78" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="C78" s="7">
+        <v>30.0</v>
+      </c>
+      <c r="D78" s="7">
+        <v>1000045.0</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F78" s="15"/>
+      <c r="G78" s="7">
+        <v>1000044.0</v>
+      </c>
+      <c r="H78" s="6">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="16"/>
-      <c r="B79" s="16"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
-      <c r="H79" s="18"/>
+      <c r="A79" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B79" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="C79" s="7">
+        <v>30.0</v>
+      </c>
+      <c r="D79" s="7">
+        <v>1000046.0</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" s="15"/>
+      <c r="G79" s="7">
+        <v>1000045.0</v>
+      </c>
+      <c r="H79" s="6">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="16"/>
-      <c r="B80" s="16"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16"/>
-      <c r="H80" s="18"/>
+      <c r="A80" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B80" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="C80" s="7">
+        <v>30.0</v>
+      </c>
+      <c r="D80" s="7">
+        <v>1000047.0</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="15"/>
+      <c r="G80" s="7">
+        <v>1000046.0</v>
+      </c>
+      <c r="H80" s="6">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="16"/>
@@ -11685,9 +11739,9 @@
       <c r="H1006" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$H$76"/>
+  <autoFilter ref="$A$1:$H$80"/>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E76">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E80">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
